--- a/Gia Phả.xlsx
+++ b/Gia Phả.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\v119618\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49A19926-3DD9-4D40-865D-CE534B45F10D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B37135CA-72DD-4F56-B931-9CF55968A175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{CF1185AB-CF45-4E41-B5D7-6E2C20922BA8}"/>
   </bookViews>
@@ -300,8 +300,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6511636" y="12366048"/>
-          <a:ext cx="10520733" cy="5935915"/>
+          <a:off x="6443600" y="12366048"/>
+          <a:ext cx="10405073" cy="5935915"/>
           <a:chOff x="41503023" y="22002750"/>
           <a:chExt cx="10299926" cy="5935915"/>
         </a:xfrm>
@@ -3327,8 +3327,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="17626804" y="12366048"/>
-          <a:ext cx="10889441" cy="4256053"/>
+          <a:off x="17436304" y="12366048"/>
+          <a:ext cx="10766977" cy="4256053"/>
           <a:chOff x="6216053" y="3858493"/>
           <a:chExt cx="10727516" cy="4256053"/>
         </a:xfrm>
@@ -6387,8 +6387,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="29110680" y="12366048"/>
-          <a:ext cx="3071983" cy="4256053"/>
+          <a:off x="28790912" y="12366048"/>
+          <a:ext cx="3044769" cy="4256053"/>
           <a:chOff x="17925873" y="3844636"/>
           <a:chExt cx="3033883" cy="4256053"/>
         </a:xfrm>
@@ -7592,8 +7592,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="32786623" y="12366048"/>
-          <a:ext cx="5561114" cy="4256053"/>
+          <a:off x="32432837" y="12366048"/>
+          <a:ext cx="5499882" cy="4256053"/>
           <a:chOff x="17465519" y="3619500"/>
           <a:chExt cx="5475389" cy="4256053"/>
         </a:xfrm>
@@ -9206,8 +9206,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="38942172" y="12366048"/>
-          <a:ext cx="4745929" cy="4256053"/>
+          <a:off x="38520351" y="12366048"/>
+          <a:ext cx="4691500" cy="4256053"/>
           <a:chOff x="21582347" y="3203864"/>
           <a:chExt cx="4631629" cy="4256053"/>
         </a:xfrm>
@@ -10589,8 +10589,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="44282536" y="12366048"/>
-          <a:ext cx="8448188" cy="4256053"/>
+          <a:off x="43799482" y="12366048"/>
+          <a:ext cx="8352938" cy="4256053"/>
           <a:chOff x="21543817" y="3619500"/>
           <a:chExt cx="8324363" cy="4256053"/>
         </a:xfrm>
@@ -12794,7 +12794,7 @@
       <xdr:col>91</xdr:col>
       <xdr:colOff>596193</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>48601</xdr:rowOff>
+      <xdr:rowOff>75815</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -12809,10 +12809,10 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="53325159" y="12366048"/>
-          <a:ext cx="3611409" cy="4256053"/>
+          <a:off x="52740052" y="12366048"/>
+          <a:ext cx="3577391" cy="4283267"/>
           <a:chOff x="15316947" y="3532909"/>
-          <a:chExt cx="3554259" cy="4256053"/>
+          <a:chExt cx="3554259" cy="4283267"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
@@ -13928,6 +13928,173 @@
           <a:xfrm>
             <a:off x="16966186" y="4019769"/>
             <a:ext cx="341178" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="293" name="Rectangle 292">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C8A5763-7914-19BD-9198-200F00888188}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="17761080" y="6916176"/>
+            <a:ext cx="635011" cy="900000"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent4">
+              <a:lumMod val="40000"/>
+              <a:lumOff val="60000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="vi-VN" sz="1100" kern="1200">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman (Headings)"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
+              </a:rPr>
+              <a:t>Nguyễn</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="vi-VN" sz="1100" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman (Headings)"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
+              </a:rPr>
+              <a:t> Minh </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman (Headings)"/>
+                <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
+              </a:rPr>
+              <a:t>Khôi</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="1100" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman (Headings)"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="294" name="Straight Connector 293">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA5C4CB1-41B4-3747-9ADA-7E4100D295BC}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="18075397" y="6501199"/>
+            <a:ext cx="0" cy="400050"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="295" name="Straight Connector 294">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B81BFD5-5FEC-11DF-EE08-CB3FED63F893}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="17569690" y="6505202"/>
+            <a:ext cx="473837" cy="0"/>
           </a:xfrm>
           <a:prstGeom prst="line">
             <a:avLst/>
@@ -13982,8 +14149,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="57531000" y="12366048"/>
-          <a:ext cx="5663828" cy="4256053"/>
+          <a:off x="56905071" y="12366048"/>
+          <a:ext cx="5595793" cy="4256053"/>
           <a:chOff x="20571653" y="3688773"/>
           <a:chExt cx="5578103" cy="4256053"/>
         </a:xfrm>
